--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:14</t>
+    <t xml:space="preserve">2026-09-09 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:09</t>
+    <t xml:space="preserve">2026-09-17 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:05</t>
+    <t xml:space="preserve">2026-09-23 12:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:34</t>
+    <t xml:space="preserve">2026-10-02 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:02</t>
+    <t xml:space="preserve">2026-10-05 10:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -688,7 +688,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>701693.12</v>
+        <v>701693.13</v>
       </c>
     </row>
     <row r="6">
@@ -739,7 +739,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>553804.62</v>
+        <v>553804.63</v>
       </c>
     </row>
     <row r="9">
@@ -841,7 +841,7 @@
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>393293.12</v>
+        <v>393293.13</v>
       </c>
     </row>
     <row r="15">
@@ -1113,7 +1113,7 @@
         <v>2019</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>324063.12</v>
+        <v>324063.13</v>
       </c>
     </row>
     <row r="31">
@@ -1147,7 +1147,7 @@
         <v>2019</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>319894.12</v>
+        <v>319894.13</v>
       </c>
     </row>
     <row r="33">
@@ -1215,7 +1215,7 @@
         <v>2019</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>286415.62</v>
+        <v>286415.63</v>
       </c>
     </row>
     <row r="37">
